--- a/examples/sample_data.xlsx
+++ b/examples/sample_data.xlsx
@@ -56,12 +56,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,12 +429,12 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -491,10 +490,10 @@
       <c r="D2" s="3" t="n">
         <v>40000</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="3">
@@ -517,10 +516,10 @@
       <c r="D3" s="3" t="n">
         <v>41500</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>4100</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="3">
@@ -543,10 +542,10 @@
       <c r="D4" s="3" t="n">
         <v>40800</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>4050</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="3" t="n">
         <v>800</v>
       </c>
       <c r="G4" s="3">
@@ -569,10 +568,10 @@
       <c r="D5" s="3" t="n">
         <v>39000</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>4150</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3">
@@ -595,10 +594,10 @@
       <c r="D6" s="3" t="n">
         <v>37800</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>4300</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="3">
@@ -621,10 +620,10 @@
       <c r="D7" s="3" t="n">
         <v>39200</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="3" t="n">
         <v>1200</v>
       </c>
       <c r="G7" s="3">
@@ -647,10 +646,10 @@
       <c r="D8" s="3" t="n">
         <v>40500</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>4450</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="3">
@@ -673,10 +672,10 @@
       <c r="D9" s="3" t="n">
         <v>38800</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>4600</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3">
@@ -699,10 +698,10 @@
       <c r="D10" s="3" t="n">
         <v>37600</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>4700</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="3" t="n">
         <v>2000</v>
       </c>
       <c r="G10" s="3">
@@ -725,10 +724,10 @@
       <c r="D11" s="3" t="n">
         <v>39500</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>4800</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="3">
@@ -751,10 +750,10 @@
       <c r="D12" s="3" t="n">
         <v>41200</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>4950</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3">
@@ -777,10 +776,10 @@
       <c r="D13" s="3" t="n">
         <v>43000</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>5100</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="G13" s="3">
@@ -803,10 +802,10 @@
       <c r="D14" s="3" t="n">
         <v>41800</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>5250</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="3">
@@ -829,10 +828,10 @@
       <c r="D15" s="3" t="n">
         <v>44200</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>5400</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="3" t="n">
         <v>1500</v>
       </c>
       <c r="G15" s="3">
@@ -855,10 +854,10 @@
       <c r="D16" s="3" t="n">
         <v>45600</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
         <v>5600</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="3">
@@ -881,10 +880,10 @@
       <c r="D17" s="3" t="n">
         <v>47000</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>5750</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="3">
@@ -907,10 +906,10 @@
       <c r="D18" s="3" t="n">
         <v>45800</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>5900</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="3" t="n">
         <v>2500</v>
       </c>
       <c r="G18" s="3">
@@ -933,10 +932,10 @@
       <c r="D19" s="3" t="n">
         <v>48200</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>6050</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="3">
